--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Stok_Toko_Alkes" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Stok_Toko_Alkes" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="140">
   <si>
     <t>nama</t>
   </si>
@@ -40,54 +40,57 @@
     <t>Thermoone</t>
   </si>
   <si>
+    <t>Termometer digital Al[pha 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Sinoheart</t>
+  </si>
+  <si>
+    <t>cek gula darah</t>
+  </si>
+  <si>
+    <t>onemed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol swab </t>
+  </si>
+  <si>
+    <t>Blood lancets</t>
+  </si>
+  <si>
+    <t>omicron</t>
+  </si>
+  <si>
+    <t>Termometer tembak</t>
+  </si>
+  <si>
+    <t>Set Rawat Luka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safegloves </t>
+  </si>
+  <si>
+    <t>Sarung Tangan M</t>
+  </si>
+  <si>
+    <t>Kotak P3K</t>
+  </si>
+  <si>
+    <t>​Ultrafix 5x1cm</t>
+  </si>
+  <si>
+    <t>Tensimeter digital</t>
+  </si>
+  <si>
+    <t>​Plesterin WP</t>
+  </si>
+  <si>
+    <t>GP care</t>
+  </si>
+  <si>
     <t xml:space="preserve">Termometer digital </t>
   </si>
   <si>
-    <t xml:space="preserve"> Sinoheart</t>
-  </si>
-  <si>
-    <t>cek gula darah</t>
-  </si>
-  <si>
-    <t>onemed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alcohol swab </t>
-  </si>
-  <si>
-    <t>Blood lancets</t>
-  </si>
-  <si>
-    <t>omicron</t>
-  </si>
-  <si>
-    <t>Termometer tembak</t>
-  </si>
-  <si>
-    <t>Set Rawat Luka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Safegloves </t>
-  </si>
-  <si>
-    <t>Sarung Tangan M</t>
-  </si>
-  <si>
-    <t>Kotak P3K</t>
-  </si>
-  <si>
-    <t>​Ultrafix 5x1cm</t>
-  </si>
-  <si>
-    <t>Tensimeter digital</t>
-  </si>
-  <si>
-    <t>​Plesterin WP</t>
-  </si>
-  <si>
-    <t>GP care</t>
-  </si>
-  <si>
     <t>LSI</t>
   </si>
   <si>
@@ -202,7 +205,7 @@
     <t>Easytouch</t>
   </si>
   <si>
-    <t>strip chole</t>
+    <t>strip chole 10</t>
   </si>
   <si>
     <t>alat penggerus</t>
@@ -235,7 +238,7 @@
     <t>Alat stik 3 in 1</t>
   </si>
   <si>
-    <t>Strip chole</t>
+    <t>Strip Asam urat 25</t>
   </si>
   <si>
     <t>Tensimeter manual</t>
@@ -308,6 +311,126 @@
   </si>
   <si>
     <t>Saturasi Oksigen</t>
+  </si>
+  <si>
+    <t>Sarung Tangan S</t>
+  </si>
+  <si>
+    <t>Sarung Tangan L</t>
+  </si>
+  <si>
+    <t>Nitril</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Nesco</t>
+  </si>
+  <si>
+    <t>GCU 3 in 1</t>
+  </si>
+  <si>
+    <t>Strip Glucosa 25</t>
+  </si>
+  <si>
+    <t>Strip Asam Urat 25</t>
+  </si>
+  <si>
+    <t>Strip Chole 10</t>
+  </si>
+  <si>
+    <t>General care</t>
+  </si>
+  <si>
+    <t>Reflex hummer</t>
+  </si>
+  <si>
+    <t>Puremed</t>
+  </si>
+  <si>
+    <t>Penlight</t>
+  </si>
+  <si>
+    <t>Nurse cap</t>
+  </si>
+  <si>
+    <t>Headcup 10</t>
+  </si>
+  <si>
+    <t>CLMK</t>
+  </si>
+  <si>
+    <t>Apron 4</t>
+  </si>
+  <si>
+    <t>Apron</t>
+  </si>
+  <si>
+    <t>ALKINDO</t>
+  </si>
+  <si>
+    <t>Masker Anak Putih 50</t>
+  </si>
+  <si>
+    <t>Masker Anak Hitam 50</t>
+  </si>
+  <si>
+    <t>Face Mask</t>
+  </si>
+  <si>
+    <t>Duckbil Hijab Hitam 50</t>
+  </si>
+  <si>
+    <t>Duckbil Hijab Putih 50</t>
+  </si>
+  <si>
+    <t>Mouson</t>
+  </si>
+  <si>
+    <t>Earloop Putih</t>
+  </si>
+  <si>
+    <t>Earloop Mix Warna</t>
+  </si>
+  <si>
+    <t>Kompres Panas Dingin</t>
+  </si>
+  <si>
+    <t>Perlak 10</t>
+  </si>
+  <si>
+    <t>AlkesPky</t>
+  </si>
+  <si>
+    <t>Tas Nursing/Medical kit Pink</t>
+  </si>
+  <si>
+    <t>Tas Nursing/Medical kit Hitam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tas Nursing/Medical kit Merah </t>
+  </si>
+  <si>
+    <t>Tas Nursing/Medical kit Abu</t>
+  </si>
+  <si>
+    <t>Tas Nursing/Medical kit Biru</t>
+  </si>
+  <si>
+    <t>Baterai AA</t>
+  </si>
+  <si>
+    <t>Baterai AAA</t>
+  </si>
+  <si>
+    <t>Thermometer digital</t>
+  </si>
+  <si>
+    <t>Saturasi A2</t>
+  </si>
+  <si>
+    <t>Saturasi rechargable</t>
   </si>
 </sst>
 </file>
@@ -378,13 +501,13 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -399,6 +522,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -649,15 +776,15 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="str">
-        <f t="shared" ref="A2:A71" si="1">F2 &amp; " - " &amp; E2
+        <f t="shared" ref="A2:A106" si="1">F2 &amp; " - " &amp; E2
 </f>
-        <v>Termometer digital  - Thermoone</v>
+        <v>Termometer digital Al[pha 1 - Thermoone</v>
       </c>
       <c r="B2" s="4">
         <v>20000.0</v>
       </c>
       <c r="C2" s="3" t="str">
-        <f t="shared" ref="C2:C71" si="2">UPPER(LEFT(F2,4) &amp; "-" &amp; LEFT(E2,2) &amp; "-" &amp; TEXT(ROW(A2)-1,"000"))
+        <f t="shared" ref="C2:C106" si="2">UPPER(LEFT(F2,4) &amp; "-" &amp; LEFT(E2,2) &amp; "-" &amp; TEXT(ROW(A2)-1,"000"))
 </f>
         <v>TERM-TH-001</v>
       </c>
@@ -721,7 +848,7 @@
         <v>13</v>
       </c>
       <c r="G4" s="7">
-        <v>9500.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="5">
@@ -746,7 +873,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="7">
-        <v>10000.0</v>
+        <v>11000.0</v>
       </c>
     </row>
     <row r="6">
@@ -770,8 +897,8 @@
       <c r="F6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="8">
-        <v>47000.0</v>
+      <c r="G6" s="7">
+        <v>40000.0</v>
       </c>
     </row>
     <row r="7">
@@ -805,7 +932,7 @@
         <v>Sarung Tangan M - Safegloves </v>
       </c>
       <c r="B8" s="4">
-        <v>45000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="C8" s="3" t="str">
         <f t="shared" si="2"/>
@@ -821,7 +948,7 @@
         <v>19</v>
       </c>
       <c r="G8" s="7">
-        <v>37000.0</v>
+        <v>45000.0</v>
       </c>
     </row>
     <row r="9">
@@ -845,7 +972,7 @@
       <c r="F9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="9">
         <v>28000.0</v>
       </c>
     </row>
@@ -870,7 +997,7 @@
       <c r="F10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="9">
         <v>3500.0</v>
       </c>
     </row>
@@ -893,7 +1020,7 @@
       <c r="F11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <v>55000.0</v>
       </c>
     </row>
@@ -918,7 +1045,7 @@
       <c r="F12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="9">
         <v>650.0</v>
       </c>
     </row>
@@ -941,9 +1068,9 @@
         <v>24</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="7">
+        <v>25</v>
+      </c>
+      <c r="G13" s="9">
         <v>16000.0</v>
       </c>
     </row>
@@ -963,12 +1090,12 @@
         <v>10.0</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="7">
+        <v>27</v>
+      </c>
+      <c r="G14" s="9">
         <v>4500.0</v>
       </c>
     </row>
@@ -988,12 +1115,12 @@
         <v>10.0</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="7">
+        <v>29</v>
+      </c>
+      <c r="G15" s="9">
         <v>7500.0</v>
       </c>
     </row>
@@ -1013,12 +1140,12 @@
         <v>10.0</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="7">
+        <v>30</v>
+      </c>
+      <c r="G16" s="9">
         <v>3000.0</v>
       </c>
     </row>
@@ -1038,12 +1165,12 @@
         <v>10.0</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="7">
+        <v>32</v>
+      </c>
+      <c r="G17" s="9">
         <v>3600.0</v>
       </c>
     </row>
@@ -1053,7 +1180,7 @@
         <v>Pulse Oximeter  - A22</v>
       </c>
       <c r="B18" s="4">
-        <v>57000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="C18" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1063,12 +1190,12 @@
         <v>10.0</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="7">
+        <v>34</v>
+      </c>
+      <c r="G18" s="9">
         <v>50000.0</v>
       </c>
     </row>
@@ -1078,7 +1205,7 @@
         <v>​Mesin Nebulizer  - omicron</v>
       </c>
       <c r="B19" s="4">
-        <v>76500.0</v>
+        <v>80000.0</v>
       </c>
       <c r="C19" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1091,9 +1218,9 @@
         <v>15</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="9">
+        <v>35</v>
+      </c>
+      <c r="G19" s="7">
         <v>40000.0</v>
       </c>
     </row>
@@ -1113,9 +1240,9 @@
         <v>10.0</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="9">
+        <v>36</v>
+      </c>
+      <c r="G20" s="7">
         <v>10000.0</v>
       </c>
     </row>
@@ -1138,9 +1265,9 @@
         <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="7">
+        <v>37</v>
+      </c>
+      <c r="G21" s="9">
         <v>110000.0</v>
       </c>
     </row>
@@ -1160,12 +1287,12 @@
         <v>10.0</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="7">
+        <v>39</v>
+      </c>
+      <c r="G22" s="9">
         <v>3650.0</v>
       </c>
     </row>
@@ -1185,12 +1312,12 @@
         <v>10.0</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G23" s="7">
+        <v>40</v>
+      </c>
+      <c r="G23" s="9">
         <v>11000.0</v>
       </c>
     </row>
@@ -1210,12 +1337,12 @@
         <v>10.0</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" s="7">
+        <v>41</v>
+      </c>
+      <c r="G24" s="9">
         <v>10000.0</v>
       </c>
     </row>
@@ -1235,12 +1362,12 @@
         <v>10.0</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G25" s="7">
+        <v>42</v>
+      </c>
+      <c r="G25" s="9">
         <v>7000.0</v>
       </c>
     </row>
@@ -1250,7 +1377,7 @@
         <v>​Syringe 50cc NT - Onemed</v>
       </c>
       <c r="B26" s="4">
-        <v>10000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="C26" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1260,12 +1387,12 @@
         <v>10.0</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" s="7">
+        <v>43</v>
+      </c>
+      <c r="G26" s="9">
         <v>6000.0</v>
       </c>
     </row>
@@ -1285,12 +1412,12 @@
         <v>10.0</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G27" s="7">
+        <v>45</v>
+      </c>
+      <c r="G27" s="9">
         <v>3650.0</v>
       </c>
     </row>
@@ -1310,12 +1437,12 @@
         <v>10.0</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G28" s="7">
+        <v>46</v>
+      </c>
+      <c r="G28" s="9">
         <v>3650.0</v>
       </c>
     </row>
@@ -1335,12 +1462,12 @@
         <v>10.0</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G29" s="7">
+        <v>48</v>
+      </c>
+      <c r="G29" s="9">
         <v>3000.0</v>
       </c>
     </row>
@@ -1360,12 +1487,12 @@
         <v>10.0</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" s="7">
+        <v>50</v>
+      </c>
+      <c r="G30" s="9">
         <v>10000.0</v>
       </c>
     </row>
@@ -1385,12 +1512,12 @@
         <v>10.0</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="9">
+        <v>52</v>
+      </c>
+      <c r="G31" s="7">
         <v>37000.0</v>
       </c>
     </row>
@@ -1410,12 +1537,12 @@
         <v>10.0</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" s="7">
+        <v>53</v>
+      </c>
+      <c r="G32" s="9">
         <v>650.0</v>
       </c>
     </row>
@@ -1435,12 +1562,12 @@
         <v>10.0</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G33" s="7">
+        <v>54</v>
+      </c>
+      <c r="G33" s="9">
         <v>600.0</v>
       </c>
     </row>
@@ -1460,12 +1587,12 @@
         <v>10.0</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="7">
+        <v>55</v>
+      </c>
+      <c r="G34" s="9">
         <v>1000.0</v>
       </c>
     </row>
@@ -1485,12 +1612,12 @@
         <v>10.0</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G35" s="7">
+        <v>56</v>
+      </c>
+      <c r="G35" s="9">
         <v>2500.0</v>
       </c>
     </row>
@@ -1500,7 +1627,7 @@
         <v>urin bag - Onemed</v>
       </c>
       <c r="B36" s="4">
-        <v>12000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="C36" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1510,12 +1637,12 @@
         <v>10.0</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="G36" s="7">
+        <v>57</v>
+      </c>
+      <c r="G36" s="9">
         <v>5500.0</v>
       </c>
     </row>
@@ -1525,7 +1652,7 @@
         <v>Needle no 24 - Terumo</v>
       </c>
       <c r="B37" s="4">
-        <v>1000.0</v>
+        <v>1500.0</v>
       </c>
       <c r="C37" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1535,13 +1662,13 @@
         <v>10.0</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G37" s="9">
-        <v>60000.0</v>
+        <v>59</v>
+      </c>
+      <c r="G37" s="7">
+        <v>600.0</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -1550,7 +1677,7 @@
         <v>Stetoskop - Onemed</v>
       </c>
       <c r="B38" s="4">
-        <v>40000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="C38" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1560,10 +1687,10 @@
         <v>10.0</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G38" s="4">
         <v>30000.0</v>
@@ -1585,10 +1712,10 @@
         <v>10.0</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G39" s="4">
         <v>11000.0</v>
@@ -1600,7 +1727,7 @@
         <v>pispot - Onemed</v>
       </c>
       <c r="B40" s="4">
-        <v>10000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="C40" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1610,19 +1737,19 @@
         <v>10.0</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G40" s="4">
-        <v>5000.0</v>
+        <v>7000.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>strip chole - Easytouch</v>
+        <v>strip chole 10 - Easytouch</v>
       </c>
       <c r="B41" s="4">
         <v>190000.0</v>
@@ -1635,10 +1762,10 @@
         <v>10.0</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G41" s="4">
         <v>160000.0</v>
@@ -1660,10 +1787,10 @@
         <v>10.0</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G42" s="4">
         <v>20000.0</v>
@@ -1685,10 +1812,10 @@
         <v>10.0</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G43" s="4">
         <v>11000.0</v>
@@ -1710,10 +1837,10 @@
         <v>10.0</v>
       </c>
       <c r="E44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="G44" s="4">
         <v>5000.0</v>
@@ -1725,7 +1852,7 @@
         <v>Tensimeter digital - Omron</v>
       </c>
       <c r="B45" s="4">
-        <v>360000.0</v>
+        <v>380000.0</v>
       </c>
       <c r="C45" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1735,7 +1862,7 @@
         <v>10.0</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>22</v>
@@ -1760,10 +1887,10 @@
         <v>10.0</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G46" s="4">
         <v>11000.0</v>
@@ -1775,7 +1902,7 @@
         <v>Tensimeter digital - Omicron</v>
       </c>
       <c r="B47" s="4">
-        <v>90000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="C47" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1785,13 +1912,13 @@
         <v>10.0</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G47" s="4">
-        <v>67000.0</v>
+        <v>70000.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
@@ -1800,7 +1927,7 @@
         <v>Strip glucosa 25 - sinoheart</v>
       </c>
       <c r="B48" s="4">
-        <v>65000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="C48" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1810,10 +1937,10 @@
         <v>10.0</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G48" s="4">
         <v>62000.0</v>
@@ -1825,7 +1952,7 @@
         <v>kasur decubitus - Onemed</v>
       </c>
       <c r="B49" s="4">
-        <v>400000.0</v>
+        <v>500000.0</v>
       </c>
       <c r="C49" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1835,13 +1962,13 @@
         <v>10.0</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G49" s="4">
-        <v>344000.0</v>
+        <v>350000.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
@@ -1860,10 +1987,10 @@
         <v>10.0</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G50" s="4">
         <v>229000.0</v>
@@ -1872,10 +1999,10 @@
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="str">
         <f t="shared" si="1"/>
-        <v>Strip chole - Easytouch</v>
+        <v>Strip Asam urat 25 - Easytouch</v>
       </c>
       <c r="B51" s="4">
-        <v>190000.0</v>
+        <v>115000.0</v>
       </c>
       <c r="C51" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1885,13 +2012,13 @@
         <v>10.0</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G51" s="4">
-        <v>160000.0</v>
+        <v>100000.0</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
@@ -1910,10 +2037,10 @@
         <v>10.0</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G52" s="4">
         <v>90000.0</v>
@@ -1925,7 +2052,7 @@
         <v>Syringe 50cc LT - Onemed</v>
       </c>
       <c r="B53" s="4">
-        <v>12000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="C53" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1935,10 +2062,10 @@
         <v>10.0</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G53" s="4">
         <v>6000.0</v>
@@ -1950,7 +2077,7 @@
         <v>urin bag - GEA</v>
       </c>
       <c r="B54" s="4">
-        <v>9000.0</v>
+        <v>10000.0</v>
       </c>
       <c r="C54" s="3" t="str">
         <f t="shared" si="2"/>
@@ -1960,10 +2087,10 @@
         <v>10.0</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54" s="4">
         <v>7000.0</v>
@@ -1985,10 +2112,10 @@
         <v>10.0</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G55" s="4">
         <v>130000.0</v>
@@ -2000,7 +2127,7 @@
         <v>Arm Sling - GlowMed</v>
       </c>
       <c r="B56" s="4">
-        <v>32000.0</v>
+        <v>35000.0</v>
       </c>
       <c r="C56" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2010,10 +2137,10 @@
         <v>10.0</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G56" s="4">
         <v>20000.0</v>
@@ -2035,10 +2162,10 @@
         <v>10.0</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G57" s="4">
         <v>1000.0</v>
@@ -2060,10 +2187,10 @@
         <v>10.0</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G58" s="4">
         <v>1000.0</v>
@@ -2085,10 +2212,10 @@
         <v>10.0</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G59" s="4">
         <v>85000.0</v>
@@ -2110,10 +2237,10 @@
         <v>10.0</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G60" s="4">
         <v>28000.0</v>
@@ -2125,7 +2252,7 @@
         <v>Oximeter saturasi - Omicron</v>
       </c>
       <c r="B61" s="4">
-        <v>130000.0</v>
+        <v>140000.0</v>
       </c>
       <c r="C61" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2135,10 +2262,10 @@
         <v>10.0</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G61" s="4">
         <v>115000.0</v>
@@ -2160,13 +2287,13 @@
         <v>10.0</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G62" s="4">
-        <v>103000.0</v>
+        <v>100000.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
@@ -2175,7 +2302,7 @@
         <v>Oximeter saturasi anak - Omicron</v>
       </c>
       <c r="B63" s="4">
-        <v>55000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="C63" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2185,10 +2312,10 @@
         <v>10.0</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G63" s="4">
         <v>45000.0</v>
@@ -2210,10 +2337,13 @@
         <v>10.0</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="G64" s="4">
+        <v>10000.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
@@ -2222,7 +2352,7 @@
         <v>Oximeter - LK88</v>
       </c>
       <c r="B65" s="4">
-        <v>50000.0</v>
+        <v>60000.0</v>
       </c>
       <c r="C65" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2232,10 +2362,10 @@
         <v>10.0</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G65" s="4">
         <v>23000.0</v>
@@ -2257,10 +2387,10 @@
         <v>10.0</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G66" s="4">
         <v>41000.0</v>
@@ -2282,7 +2412,7 @@
         <v>10.0</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>22</v>
@@ -2307,10 +2437,10 @@
         <v>10.0</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G68" s="4">
         <v>100000.0</v>
@@ -2332,13 +2462,13 @@
         <v>10.0</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>22</v>
       </c>
       <c r="G69" s="4">
-        <v>155000.0</v>
+        <v>180000.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
@@ -2347,7 +2477,7 @@
         <v>Saturasi Oksigen - Omicron</v>
       </c>
       <c r="B70" s="4">
-        <v>120000.0</v>
+        <v>140000.0</v>
       </c>
       <c r="C70" s="3" t="str">
         <f t="shared" si="2"/>
@@ -2357,10 +2487,10 @@
         <v>10.0</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G70" s="4">
         <v>115000.0</v>
@@ -2382,50 +2512,869 @@
         <v>2.0</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G71" s="4">
         <v>187000.0</v>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Sarung Tangan S - Safegloves </v>
+      </c>
+      <c r="B72" s="4">
+        <v>60000.0</v>
+      </c>
+      <c r="C72" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SARU-SA-071</v>
+      </c>
+      <c r="D72" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G72" s="4">
+        <v>45000.0</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Sarung Tangan L - Safegloves </v>
+      </c>
+      <c r="B73" s="4">
+        <v>60000.0</v>
+      </c>
+      <c r="C73" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SARU-SA-072</v>
+      </c>
+      <c r="D73" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G73" s="4">
+        <v>45000.0</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Sarung Tangan S - Nitril</v>
+      </c>
+      <c r="B74" s="4">
+        <v>70000.0</v>
+      </c>
+      <c r="C74" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SARU-NI-073</v>
+      </c>
+      <c r="D74" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G74" s="4">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Sarung Tangan L - Nitril</v>
+      </c>
+      <c r="B75" s="4">
+        <v>70000.0</v>
+      </c>
+      <c r="C75" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SARU-NI-074</v>
+      </c>
+      <c r="D75" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="G75" s="4">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Sarung Tangan M - Nitril</v>
+      </c>
+      <c r="B76" s="4">
+        <v>70000.0</v>
+      </c>
+      <c r="C76" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SARU-NI-075</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G76" s="4">
+        <v>60000.0</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Tensimeter BW750 - -</v>
+      </c>
+      <c r="B77" s="4">
+        <v>120000.0</v>
+      </c>
+      <c r="C77" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TENS---076</v>
+      </c>
+      <c r="D77" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G77" s="4">
+        <v>85000.0</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>GCU 3 in 1 - Nesco</v>
+      </c>
+      <c r="B78" s="4">
+        <v>300000.0</v>
+      </c>
+      <c r="C78" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>GCU -NE-077</v>
+      </c>
+      <c r="D78" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="G78" s="4">
+        <v>240000.0</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Strip Glucosa 25 - Nesco</v>
+      </c>
+      <c r="B79" s="4">
+        <v>120000.0</v>
+      </c>
+      <c r="C79" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>STRI-NE-078</v>
+      </c>
+      <c r="D79" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G79" s="4">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Strip Asam Urat 25 - Nesco</v>
+      </c>
+      <c r="B80" s="4">
+        <v>115000.0</v>
+      </c>
+      <c r="C80" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>STRI-NE-079</v>
+      </c>
+      <c r="D80" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G80" s="4">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Strip Chole 10 - Nesco</v>
+      </c>
+      <c r="B81" s="4">
+        <v>200000.0</v>
+      </c>
+      <c r="C81" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>STRI-NE-080</v>
+      </c>
+      <c r="D81" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G81" s="4">
+        <v>190000.0</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Strip Glucosa 25 - Easytouch</v>
+      </c>
+      <c r="B82" s="4">
+        <v>120000.0</v>
+      </c>
+      <c r="C82" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>STRI-EA-081</v>
+      </c>
+      <c r="D82" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G82" s="4">
+        <v>100000.0</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Reflex hummer - General care</v>
+      </c>
+      <c r="B83" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="C83" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>REFL-GE-082</v>
+      </c>
+      <c r="D83" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G83" s="4">
+        <v>25000.0</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Penlight - Puremed</v>
+      </c>
+      <c r="B84" s="4">
+        <v>55000.0</v>
+      </c>
+      <c r="C84" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PENL-PU-083</v>
+      </c>
+      <c r="D84" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G84" s="4">
+        <v>35000.0</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Nurse cap - </v>
+      </c>
+      <c r="B85" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="C85" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NURS--084</v>
+      </c>
+      <c r="D85" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G85" s="4">
+        <v>25000.0</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Headcup 10 - onemed</v>
+      </c>
+      <c r="B86" s="4">
+        <v>10000.0</v>
+      </c>
+      <c r="C86" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>HEAD-ON-085</v>
+      </c>
+      <c r="D86" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G86" s="4">
+        <v>3600.0</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Apron 4 - CLMK</v>
+      </c>
+      <c r="B87" s="4">
+        <v>10000.0</v>
+      </c>
+      <c r="C87" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>APRO-CL-086</v>
+      </c>
+      <c r="D87" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G87" s="4">
+        <v>6400.0</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Apron - CLMK</v>
+      </c>
+      <c r="B88" s="4">
+        <v>2500.0</v>
+      </c>
+      <c r="C88" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>APRO-CL-087</v>
+      </c>
+      <c r="D88" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G88" s="4">
+        <v>2500.0</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Masker Anak Putih 50 - ALKINDO</v>
+      </c>
+      <c r="B89" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="C89" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MASK-AL-088</v>
+      </c>
+      <c r="D89" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G89" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Masker Anak Hitam 50 - ALKINDO</v>
+      </c>
+      <c r="B90" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="C90" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>MASK-AL-089</v>
+      </c>
+      <c r="D90" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G90" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Duckbil Hijab Hitam 50 - Face Mask</v>
+      </c>
+      <c r="B91" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C91" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>DUCK-FA-090</v>
+      </c>
+      <c r="D91" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G91" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Duckbil Hijab Putih 50 - Face Mask</v>
+      </c>
+      <c r="B92" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C92" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>DUCK-FA-091</v>
+      </c>
+      <c r="D92" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="G92" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Earloop Putih - Mouson</v>
+      </c>
+      <c r="B93" s="4">
+        <v>20000.0</v>
+      </c>
+      <c r="C93" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>EARL-MO-092</v>
+      </c>
+      <c r="D93" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="G93" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Earloop Mix Warna - Mouson</v>
+      </c>
+      <c r="B94" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C94" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>EARL-MO-093</v>
+      </c>
+      <c r="D94" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G94" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Kompres Panas Dingin - </v>
+      </c>
+      <c r="B95" s="4">
+        <v>35000.0</v>
+      </c>
+      <c r="C95" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>KOMP--094</v>
+      </c>
+      <c r="D95" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G95" s="4">
+        <v>25000.0</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Perlak 10 - Onemed</v>
+      </c>
+      <c r="B96" s="4">
+        <v>40000.0</v>
+      </c>
+      <c r="C96" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>PERL-ON-095</v>
+      </c>
+      <c r="D96" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G96" s="4">
+        <v>30000.0</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Tas Nursing/Medical kit Pink - AlkesPky</v>
+      </c>
+      <c r="B97" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C97" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TAS -AL-096</v>
+      </c>
+      <c r="D97" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G97" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Tas Nursing/Medical kit Hitam - AlkesPky</v>
+      </c>
+      <c r="B98" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C98" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TAS -AL-097</v>
+      </c>
+      <c r="D98" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="G98" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Tas Nursing/Medical kit Merah  - AlkesPky</v>
+      </c>
+      <c r="B99" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C99" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TAS -AL-098</v>
+      </c>
+      <c r="D99" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G99" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Tas Nursing/Medical kit Abu - AlkesPky</v>
+      </c>
+      <c r="B100" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C100" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TAS -AL-099</v>
+      </c>
+      <c r="D100" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G100" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Tas Nursing/Medical kit Biru - AlkesPky</v>
+      </c>
+      <c r="B101" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C101" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TAS -AL-100</v>
+      </c>
+      <c r="D101" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G101" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Baterai AA - </v>
+      </c>
+      <c r="B102" s="4">
+        <v>4000.0</v>
+      </c>
+      <c r="C102" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>BATE--101</v>
+      </c>
+      <c r="D102" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G102" s="4">
+        <v>2000.0</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Baterai AAA - </v>
+      </c>
+      <c r="B103" s="4">
+        <v>4000.0</v>
+      </c>
+      <c r="C103" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>BATE--102</v>
+      </c>
+      <c r="D103" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G103" s="4">
+        <v>2000.0</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Thermometer digital - Omron</v>
+      </c>
+      <c r="B104" s="4">
+        <v>90000.0</v>
+      </c>
+      <c r="C104" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>THER-OM-103</v>
+      </c>
+      <c r="D104" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G104" s="4">
+        <v>70000.0</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Saturasi A2 - </v>
+      </c>
+      <c r="B105" s="4">
+        <v>70000.0</v>
+      </c>
+      <c r="C105" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SATU--104</v>
+      </c>
+      <c r="D105" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G105" s="4">
+        <v>40000.0</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Saturasi rechargable - </v>
+      </c>
+      <c r="B106" s="4">
+        <v>100000.0</v>
+      </c>
+      <c r="C106" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>SATU--105</v>
+      </c>
+      <c r="D106" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G106" s="4">
+        <v>70000.0</v>
+      </c>
+    </row>
     <row r="107" ht="15.75" customHeight="1"/>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="141">
   <si>
     <t>nama</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Thermoone</t>
   </si>
   <si>
-    <t>Termometer digital Al[pha 1</t>
+    <t>Termometer digital Alpha 1</t>
   </si>
   <si>
     <t xml:space="preserve"> Sinoheart</t>
@@ -431,6 +431,9 @@
   </si>
   <si>
     <t>Saturasi rechargable</t>
+  </si>
+  <si>
+    <t>Termometer digital Alpha 2</t>
   </si>
 </sst>
 </file>
@@ -729,13 +732,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="33.29"/>
-    <col customWidth="1" min="2" max="2" width="12.57"/>
-    <col customWidth="1" min="3" max="3" width="15.57"/>
+    <col customWidth="1" min="1" max="1" width="37.43"/>
+    <col customWidth="1" min="2" max="2" width="10.0"/>
+    <col customWidth="1" min="3" max="3" width="14.43"/>
     <col customWidth="1" min="4" max="4" width="7.0"/>
     <col customWidth="1" min="5" max="5" width="15.0"/>
-    <col customWidth="1" min="6" max="6" width="29.14"/>
-    <col customWidth="1" min="7" max="7" width="18.0"/>
+    <col customWidth="1" min="6" max="6" width="25.29"/>
+    <col customWidth="1" min="7" max="7" width="11.43"/>
     <col customWidth="1" min="8" max="8" width="19.71"/>
     <col customWidth="1" min="9" max="9" width="12.0"/>
     <col customWidth="1" min="10" max="10" width="20.0"/>
@@ -776,15 +779,15 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="str">
-        <f t="shared" ref="A2:A106" si="1">F2 &amp; " - " &amp; E2
+        <f t="shared" ref="A2:A107" si="1">F2 &amp; " - " &amp; E2
 </f>
-        <v>Termometer digital Al[pha 1 - Thermoone</v>
+        <v>Termometer digital Alpha 1 - Thermoone</v>
       </c>
       <c r="B2" s="4">
         <v>20000.0</v>
       </c>
       <c r="C2" s="3" t="str">
-        <f t="shared" ref="C2:C106" si="2">UPPER(LEFT(F2,4) &amp; "-" &amp; LEFT(E2,2) &amp; "-" &amp; TEXT(ROW(A2)-1,"000"))
+        <f t="shared" ref="C2:C107" si="2">UPPER(LEFT(F2,4) &amp; "-" &amp; LEFT(E2,2) &amp; "-" &amp; TEXT(ROW(A2)-1,"000"))
 </f>
         <v>TERM-TH-001</v>
       </c>
@@ -3375,7 +3378,31 @@
         <v>70000.0</v>
       </c>
     </row>
-    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>Termometer digital Alpha 2 - Thermoone</v>
+      </c>
+      <c r="B107" s="4">
+        <v>25000.0</v>
+      </c>
+      <c r="C107" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>TERM-TH-106</v>
+      </c>
+      <c r="D107" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G107" s="4">
+        <v>15000.0</v>
+      </c>
+    </row>
     <row r="108" ht="15.75" customHeight="1"/>
     <row r="109" ht="15.75" customHeight="1"/>
     <row r="110" ht="15.75" customHeight="1"/>
